--- a/data/trans_bre/P23_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P23_R-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,82; -5,07</t>
+          <t>-21,17; -4,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,98; -3,76</t>
+          <t>-20,14; -2,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,13; -3,25</t>
+          <t>-18,67; -3,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-48,26; -13,8</t>
+          <t>-47,36; -13,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -8,32</t>
+          <t>-40,09; -7,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,54; -10,11</t>
+          <t>-45,66; -10,55</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,6; -9,81</t>
+          <t>-21,42; -9,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,79; -6,08</t>
+          <t>-17,9; -5,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,74; -8,38</t>
+          <t>-20,16; -7,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,45; -26,9</t>
+          <t>-50,72; -26,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,9; -15,65</t>
+          <t>-40,63; -15,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,4; -21,56</t>
+          <t>-45,27; -20,75</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -10,99</t>
+          <t>-26,21; -10,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,02; -5,82</t>
+          <t>-20,33; -6,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 0,84</t>
+          <t>-12,99; 0,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-50,26; -25,83</t>
+          <t>-51,34; -24,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,54; -15,52</t>
+          <t>-48,08; -16,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,73; 3,67</t>
+          <t>-38,36; 1,99</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,7; -12,55</t>
+          <t>-25,96; -12,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -1,61</t>
+          <t>-15,44; -2,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,9; -2,68</t>
+          <t>-17,43; -3,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,15; -27,55</t>
+          <t>-51,06; -27,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,72; -4,63</t>
+          <t>-39,45; -6,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,1; -7,82</t>
+          <t>-41,18; -9,98</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,81; -3,55</t>
+          <t>-21,78; -3,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,24; -3,56</t>
+          <t>-22,17; -3,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,24; -5,99</t>
+          <t>-23,72; -5,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-48,39; -9,8</t>
+          <t>-46,7; -9,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,47; -8,36</t>
+          <t>-47,4; -9,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-51,33; -15,51</t>
+          <t>-52,18; -16,93</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,28; -15,01</t>
+          <t>-30,21; -14,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 0,91</t>
+          <t>-13,93; 1,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 0,8</t>
+          <t>-15,45; 0,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,46; -35,59</t>
+          <t>-60,24; -34,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 4,53</t>
+          <t>-39,68; 6,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,78; 2,76</t>
+          <t>-40,68; 3,35</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,39; -7,85</t>
+          <t>-17,89; -7,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -8,86</t>
+          <t>-19,7; -9,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -0,31</t>
+          <t>-10,41; -0,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-44,75; -22,39</t>
+          <t>-43,99; -21,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-42,98; -22,97</t>
+          <t>-43,23; -22,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,49; -0,91</t>
+          <t>-31,01; 0,27</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,58; -13,46</t>
+          <t>-23,9; -13,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,31; -7,77</t>
+          <t>-17,34; -8,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,26; -2,17</t>
+          <t>-11,38; -1,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-52,67; -33,96</t>
+          <t>-52,49; -34,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,71; -21,52</t>
+          <t>-42,41; -22,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,5; -7,05</t>
+          <t>-33,12; -6,66</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-18,98; -14,32</t>
+          <t>-19,08; -14,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,31; -9,69</t>
+          <t>-14,42; -9,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,0; -6,66</t>
+          <t>-11,2; -6,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-43,56; -34,82</t>
+          <t>-43,64; -35,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-35,21; -25,25</t>
+          <t>-35,28; -25,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -19,66</t>
+          <t>-30,72; -19,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P23_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P23_R-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,17; -4,93</t>
+          <t>-21,99; -5,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,14; -2,9</t>
+          <t>-20,36; -3,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,67; -3,39</t>
+          <t>-18,54; -3,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-47,36; -13,09</t>
+          <t>-47,91; -13,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,09; -7,12</t>
+          <t>-40,88; -8,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,66; -10,55</t>
+          <t>-45,9; -9,21</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,42; -9,81</t>
+          <t>-21,6; -9,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,9; -5,99</t>
+          <t>-18,56; -6,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,16; -7,79</t>
+          <t>-20,32; -8,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,72; -26,66</t>
+          <t>-50,36; -26,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,63; -15,75</t>
+          <t>-41,58; -16,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,27; -20,75</t>
+          <t>-45,37; -22,73</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,21; -10,61</t>
+          <t>-26,47; -11,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -6,09</t>
+          <t>-20,97; -5,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 0,64</t>
+          <t>-13,13; 1,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-51,34; -24,64</t>
+          <t>-52,14; -25,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,08; -16,88</t>
+          <t>-49,62; -16,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 1,99</t>
+          <t>-39,43; 5,2</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,96; -12,49</t>
+          <t>-25,75; -12,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,44; -2,03</t>
+          <t>-15,08; -0,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,43; -3,48</t>
+          <t>-16,69; -2,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,06; -27,96</t>
+          <t>-50,57; -27,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,45; -6,24</t>
+          <t>-38,82; 0,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,18; -9,98</t>
+          <t>-40,1; -6,28</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,78; -3,91</t>
+          <t>-22,16; -3,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,17; -3,25</t>
+          <t>-22,26; -3,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,72; -5,83</t>
+          <t>-23,43; -5,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-46,7; -9,72</t>
+          <t>-47,82; -7,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,4; -9,12</t>
+          <t>-46,93; -10,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-52,18; -16,93</t>
+          <t>-51,64; -14,85</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,21; -14,58</t>
+          <t>-30,69; -14,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 1,6</t>
+          <t>-15,14; -0,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 0,93</t>
+          <t>-15,09; 1,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,24; -34,45</t>
+          <t>-61,73; -35,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,68; 6,73</t>
+          <t>-42,46; -0,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 3,35</t>
+          <t>-39,68; 3,96</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,89; -7,97</t>
+          <t>-18,44; -7,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,7; -9,08</t>
+          <t>-19,59; -9,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -0,14</t>
+          <t>-10,92; -0,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-43,99; -21,43</t>
+          <t>-44,38; -20,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,23; -22,48</t>
+          <t>-43,03; -22,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 0,27</t>
+          <t>-31,1; -2,11</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,9; -13,6</t>
+          <t>-22,99; -13,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,34; -8,03</t>
+          <t>-17,83; -7,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,38; -1,89</t>
+          <t>-11,73; -1,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-52,49; -34,16</t>
+          <t>-51,95; -34,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,41; -22,29</t>
+          <t>-43,44; -21,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,12; -6,66</t>
+          <t>-33,25; -6,39</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -14,65</t>
+          <t>-18,96; -14,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -9,74</t>
+          <t>-14,4; -9,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,2; -6,65</t>
+          <t>-11,33; -6,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-43,64; -35,66</t>
+          <t>-43,67; -35,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-35,28; -25,5</t>
+          <t>-35,29; -25,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,72; -19,76</t>
+          <t>-31,15; -19,86</t>
         </is>
       </c>
     </row>
